--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -653,187 +653,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F8" s="3">
         <v>29300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>29400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>30000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>32500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>33700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>37200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>35300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>37500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>38300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>34100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F9" s="3">
         <v>18300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>17500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>18100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>19600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>20400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>21800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>22700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>24200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>24100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>20500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F10" s="3">
         <v>11000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>11900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>11900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>12900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>13300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>15400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>12600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>13300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>14200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>13600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,46 +873,54 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="E12" s="3">
         <v>1200</v>
       </c>
       <c r="F12" s="3">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="G12" s="3">
         <v>1200</v>
       </c>
       <c r="H12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -924,46 +957,58 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3">
+        <v>42700</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-2200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -971,37 +1016,43 @@
         <v>3900</v>
       </c>
       <c r="E15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G15" s="3">
         <v>3300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>3000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>3000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>3100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1013,84 +1064,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F17" s="3">
         <v>31300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>30700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>30200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>31600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>32000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>34500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>34100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>33600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>36900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>34200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1105,84 +1170,98 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="G20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="F21" s="3">
         <v>1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>5000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1190,16 +1269,16 @@
         <v>400</v>
       </c>
       <c r="E22" s="3">
+        <v>400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>400</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1208,71 +1287,83 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>-600</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
@@ -1284,19 +1375,25 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+        <v>-200</v>
+      </c>
+      <c r="O24" s="3">
+        <v>200</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1333,84 +1430,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2700</v>
       </c>
       <c r="J26" s="3">
         <v>1100</v>
       </c>
       <c r="K26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M26" s="3">
         <v>3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1447,8 +1562,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1485,8 +1606,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1523,8 +1650,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1561,84 +1694,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G32" s="3">
+        <v>200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1675,89 +1826,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1772,8 +1941,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1788,46 +1959,54 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F41" s="3">
         <v>6400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1864,46 +2043,58 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F43" s="3">
         <v>17300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>16900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>19700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>19200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>20700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>23700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>23200</v>
-      </c>
-      <c r="K43" s="3">
-        <v>21700</v>
-      </c>
-      <c r="L43" s="3">
-        <v>22800</v>
       </c>
       <c r="M43" s="3">
         <v>21700</v>
       </c>
       <c r="N43" s="3">
+        <v>22800</v>
+      </c>
+      <c r="O43" s="3">
+        <v>21700</v>
+      </c>
+      <c r="P43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -1911,16 +2102,16 @@
         <v>500</v>
       </c>
       <c r="E44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F44" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G44" s="3">
         <v>400</v>
       </c>
       <c r="H44" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I44" s="3">
         <v>400</v>
@@ -1929,95 +2120,113 @@
         <v>400</v>
       </c>
       <c r="K44" s="3">
+        <v>400</v>
+      </c>
+      <c r="L44" s="3">
+        <v>400</v>
+      </c>
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F46" s="3">
         <v>27500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>27800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>31500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>34700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>37600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>36800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>35600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>36400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>34900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2054,84 +2263,102 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F48" s="3">
         <v>9800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>10000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>10300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>11900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>12300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>12200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>13300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>44300</v>
+      </c>
+      <c r="F49" s="3">
         <v>87900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>89100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>89700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>90700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>90900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>91400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>91700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>92000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>92800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>93900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2168,8 +2395,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,22 +2439,28 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>600</v>
+      </c>
+      <c r="F52" s="3">
         <v>700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>800</v>
       </c>
       <c r="H52" s="3">
         <v>800</v>
@@ -2230,22 +2469,28 @@
         <v>800</v>
       </c>
       <c r="J52" s="3">
+        <v>800</v>
+      </c>
+      <c r="K52" s="3">
+        <v>800</v>
+      </c>
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2282,46 +2527,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>77800</v>
+      </c>
+      <c r="F54" s="3">
         <v>125900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>126800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>131000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>136200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>131200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>140100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>141200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>140800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>142500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>143400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2336,8 +2593,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2352,236 +2611,274 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>5900</v>
       </c>
       <c r="L57" s="3">
         <v>5800</v>
       </c>
       <c r="M57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="N57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O57" s="3">
         <v>4800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>300</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F59" s="3">
         <v>15200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>14400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>13900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>16400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>19400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>21100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>22200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>23300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>20100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>22200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F60" s="3">
         <v>21900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>19200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>22400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>24600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>26200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>28100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>29600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>26500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>26900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="E61" s="3">
         <v>10000</v>
       </c>
       <c r="F61" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G61" s="3">
         <v>10000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I61" s="3">
         <v>8000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>7000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>6000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>8000</v>
       </c>
       <c r="L61" s="3">
         <v>6000</v>
       </c>
       <c r="M61" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N61" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O61" s="3">
         <v>5000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>13000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>13600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2618,8 +2915,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2656,8 +2959,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2694,46 +3003,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>36100</v>
+      </c>
+      <c r="F66" s="3">
         <v>37800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>33300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>32900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>34500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>28400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>37400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>38900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>42900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>45500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>45600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2748,8 +3069,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2786,8 +3109,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2824,8 +3153,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2862,8 +3197,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2900,46 +3241,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-74500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-30800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-28000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-25600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-26100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-29900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-31100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-34600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-36100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2976,8 +3329,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3014,8 +3373,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3052,46 +3417,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F76" s="3">
         <v>88100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>93500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>98100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>101700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>102800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>102700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>102300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>97900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>97000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>97800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3128,89 +3505,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-47600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3225,8 +3620,10 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -3234,37 +3631,43 @@
         <v>4000</v>
       </c>
       <c r="E83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G83" s="3">
         <v>3500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>3100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>3100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>3700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>3200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3301,8 +3704,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3339,8 +3748,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3377,8 +3792,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3415,8 +3836,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3453,46 +3880,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F89" s="3">
         <v>4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>6400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>6100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3507,46 +3946,54 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3583,8 +4030,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3621,46 +4074,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-2900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-14800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3675,8 +4140,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -3713,8 +4180,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3751,8 +4224,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3789,8 +4268,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3827,118 +4312,142 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-9000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-300</v>
       </c>
       <c r="K100" s="3">
         <v>-1800</v>
       </c>
       <c r="L100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>1000</v>
       </c>
       <c r="L102" s="3">
         <v>-200</v>
       </c>
       <c r="M102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O102" s="3">
         <v>-11500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -653,124 +653,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E8" s="3">
         <v>26000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,87 +785,93 @@
         <v>15200</v>
       </c>
       <c r="E9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F9" s="3">
         <v>17000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E10" s="3">
         <v>10800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>11900</v>
       </c>
       <c r="H10" s="3">
         <v>11900</v>
       </c>
       <c r="I10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="J10" s="3">
         <v>12900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,52 +888,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1200</v>
       </c>
       <c r="J12" s="3">
         <v>1200</v>
       </c>
       <c r="K12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,96 +980,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>42700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3000</v>
       </c>
       <c r="I15" s="3">
         <v>3000</v>
       </c>
       <c r="J15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K15" s="3">
         <v>2800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>2900</v>
       </c>
       <c r="L15" s="3">
         <v>2900</v>
       </c>
       <c r="M15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,8 +1092,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1075,87 +1102,93 @@
         <v>25800</v>
       </c>
       <c r="E17" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F17" s="3">
         <v>72000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1172,101 +1205,108 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-39700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
@@ -1275,13 +1315,13 @@
         <v>400</v>
       </c>
       <c r="G22" s="3">
+        <v>400</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1293,10 +1333,10 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1304,52 +1344,58 @@
       <c r="P22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-44300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1357,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
@@ -1369,31 +1415,34 @@
         <v>100</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1436,96 +1485,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-43700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1568,8 +1626,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1612,8 +1673,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1656,8 +1720,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1700,96 +1767,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1832,101 +1908,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1943,8 +2028,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1961,52 +2047,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
         <v>4100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2049,52 +2139,58 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E43" s="3">
         <v>17400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2108,13 +2204,13 @@
         <v>500</v>
       </c>
       <c r="G44" s="3">
+        <v>500</v>
+      </c>
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
-      </c>
-      <c r="I44" s="3">
-        <v>400</v>
       </c>
       <c r="J44" s="3">
         <v>400</v>
@@ -2126,107 +2222,116 @@
         <v>400</v>
       </c>
       <c r="M44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N44" s="3">
         <v>500</v>
       </c>
       <c r="O44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>4800</v>
       </c>
       <c r="O45" s="3">
         <v>4800</v>
       </c>
       <c r="P45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E46" s="3">
         <v>24300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2269,96 +2374,105 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E48" s="3">
         <v>9500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E49" s="3">
         <v>42400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>44300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>87900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>89100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>89700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>90700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>90900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>91400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>91700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>92000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>92800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>93900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2401,8 +2515,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2445,8 +2562,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -2457,13 +2577,13 @@
         <v>600</v>
       </c>
       <c r="F52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G52" s="3">
         <v>700</v>
       </c>
       <c r="H52" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="I52" s="3">
         <v>800</v>
@@ -2475,22 +2595,25 @@
         <v>800</v>
       </c>
       <c r="L52" s="3">
+        <v>800</v>
+      </c>
+      <c r="M52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2533,52 +2656,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E54" s="3">
         <v>76900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>77800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>126800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>131000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>136200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>131200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>140100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>141200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>140800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>142500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>143400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2595,8 +2724,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2613,96 +2743,103 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5200</v>
       </c>
       <c r="H57" s="3">
         <v>5200</v>
       </c>
       <c r="I57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
@@ -2710,175 +2847,187 @@
         <v>17700</v>
       </c>
       <c r="E59" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F59" s="3">
         <v>17200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E60" s="3">
         <v>23800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>10000</v>
       </c>
       <c r="H61" s="3">
         <v>10000</v>
       </c>
       <c r="I61" s="3">
+        <v>10000</v>
+      </c>
+      <c r="J61" s="3">
         <v>8000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>7000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3700</v>
       </c>
       <c r="H62" s="3">
         <v>3700</v>
       </c>
       <c r="I62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2921,8 +3070,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2965,8 +3117,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3009,52 +3164,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E66" s="3">
         <v>35500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>34500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>42900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3071,8 +3232,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3115,8 +3277,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3159,8 +3324,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3203,8 +3371,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3247,52 +3418,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-74700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-74500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-30800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-26200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-26100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-29900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-34600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-36100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3335,8 +3512,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3379,8 +3559,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3423,52 +3606,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E76" s="3">
         <v>41400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>93500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>98100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>102800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>102700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>97900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3511,101 +3700,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3622,52 +3820,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E83" s="3">
         <v>4000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3200</v>
       </c>
       <c r="I83" s="3">
         <v>3200</v>
       </c>
       <c r="J83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K83" s="3">
         <v>3000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>3100</v>
       </c>
       <c r="L83" s="3">
         <v>3100</v>
       </c>
       <c r="M83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N83" s="3">
         <v>2800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3710,8 +3912,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3754,8 +3959,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3798,8 +4006,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3842,8 +4053,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3886,52 +4100,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3948,52 +4168,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-3000</v>
       </c>
       <c r="H91" s="3">
         <v>-3000</v>
       </c>
       <c r="I91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-2800</v>
       </c>
       <c r="L91" s="3">
         <v>-2800</v>
       </c>
       <c r="M91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4036,8 +4260,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4080,52 +4307,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-3000</v>
       </c>
       <c r="H94" s="3">
         <v>-3000</v>
       </c>
       <c r="I94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-2800</v>
       </c>
       <c r="L94" s="3">
         <v>-2800</v>
       </c>
       <c r="M94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="N94" s="3">
         <v>-3300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4142,8 +4375,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -4186,8 +4420,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4230,8 +4467,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4274,8 +4514,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4318,136 +4561,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>CCLD</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,225 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E8" s="3">
         <v>28100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>37200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15200</v>
+        <v>15400</v>
       </c>
       <c r="E9" s="3">
         <v>15200</v>
       </c>
       <c r="F9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="G9" s="3">
         <v>17000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12900</v>
+        <v>13100</v>
       </c>
       <c r="E10" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F10" s="3">
         <v>10800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>11900</v>
       </c>
       <c r="I10" s="3">
         <v>11900</v>
       </c>
       <c r="J10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K10" s="3">
         <v>12900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>1100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1200</v>
       </c>
       <c r="K12" s="3">
         <v>1200</v>
       </c>
       <c r="L12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -983,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -992,93 +1015,99 @@
         <v>100</v>
       </c>
       <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>42700</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O14" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="P14" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
-        <v>300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-400</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="O14" s="3">
-        <v>400</v>
-      </c>
-      <c r="P14" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E15" s="3">
         <v>3700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3000</v>
       </c>
       <c r="J15" s="3">
         <v>3000</v>
       </c>
       <c r="K15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L15" s="3">
         <v>2800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2900</v>
       </c>
       <c r="M15" s="3">
         <v>2900</v>
       </c>
       <c r="N15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>25800</v>
+        <v>25200</v>
       </c>
       <c r="E17" s="3">
-        <v>25800</v>
+        <v>25700</v>
       </c>
       <c r="F17" s="3">
-        <v>72000</v>
+        <v>25500</v>
       </c>
       <c r="G17" s="3">
-        <v>31300</v>
+        <v>29400</v>
       </c>
       <c r="H17" s="3">
-        <v>30700</v>
+        <v>31200</v>
       </c>
       <c r="I17" s="3">
-        <v>30200</v>
+        <v>30500</v>
       </c>
       <c r="J17" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K17" s="3">
         <v>31600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="E18" s="3">
-        <v>200</v>
+        <v>2400</v>
       </c>
       <c r="F18" s="3">
-        <v>-43600</v>
+        <v>500</v>
       </c>
       <c r="G18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
-        <v>-1300</v>
-      </c>
       <c r="I18" s="3">
-        <v>-200</v>
+        <v>-1100</v>
       </c>
       <c r="J18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K18" s="3">
         <v>900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1206,110 +1242,117 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E21" s="3">
         <v>5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L21" s="3">
         <v>4200</v>
       </c>
-      <c r="F21" s="3">
-        <v>-39700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
-      </c>
-      <c r="E22" s="3">
-        <v>400</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
@@ -1318,13 +1361,13 @@
         <v>400</v>
       </c>
       <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1336,10 +1379,10 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -1347,55 +1390,61 @@
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-44300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1406,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
@@ -1418,31 +1467,34 @@
         <v>100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1488,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-43700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
-        <v>-200</v>
-      </c>
       <c r="F27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G27" s="3">
         <v>-47600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1629,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1676,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1723,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1770,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-2200</v>
+        <v>3100</v>
       </c>
       <c r="E33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
-        <v>-47600</v>
-      </c>
       <c r="G33" s="3">
-        <v>-6700</v>
+        <v>-43700</v>
       </c>
       <c r="H33" s="3">
-        <v>-5700</v>
+        <v>-2700</v>
       </c>
       <c r="I33" s="3">
-        <v>-4300</v>
+        <v>-1800</v>
       </c>
       <c r="J33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1911,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-2200</v>
+        <v>3100</v>
       </c>
       <c r="E35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
-        <v>-47600</v>
-      </c>
       <c r="G35" s="3">
-        <v>-6700</v>
+        <v>-43700</v>
       </c>
       <c r="H35" s="3">
-        <v>-5700</v>
+        <v>-2700</v>
       </c>
       <c r="I35" s="3">
-        <v>-4300</v>
+        <v>-1800</v>
       </c>
       <c r="J35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2029,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2048,55 +2137,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2142,55 +2235,61 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E43" s="3">
         <v>17900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2207,13 +2306,13 @@
         <v>500</v>
       </c>
       <c r="H44" s="3">
+        <v>500</v>
+      </c>
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>400</v>
@@ -2225,136 +2324,145 @@
         <v>400</v>
       </c>
       <c r="N44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O44" s="3">
         <v>500</v>
       </c>
       <c r="P44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>2900</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>4800</v>
       </c>
       <c r="P45" s="3">
         <v>4800</v>
       </c>
       <c r="Q45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="R45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E46" s="3">
         <v>23900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2377,102 +2485,111 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E48" s="3">
         <v>8800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E49" s="3">
         <v>40700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>42400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>44300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>87900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>89100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>89700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>90700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>90900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>91400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>91700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>92000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>92800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>93900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2518,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2565,31 +2685,34 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>800</v>
@@ -2598,22 +2721,25 @@
         <v>800</v>
       </c>
       <c r="M52" s="3">
+        <v>800</v>
+      </c>
+      <c r="N52" s="3">
         <v>900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2659,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E54" s="3">
         <v>74000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>77800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>126800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>131000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>136200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>131200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>140100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>141200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>140800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>142500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>143400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2725,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2744,290 +2877,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5200</v>
       </c>
       <c r="I57" s="3">
         <v>5200</v>
       </c>
       <c r="J57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K58" s="3">
+        <v>300</v>
+      </c>
+      <c r="L58" s="3">
+        <v>600</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
-        <v>300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>300</v>
-      </c>
-      <c r="O58" s="3">
-        <v>600</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>17700</v>
+        <v>7000</v>
       </c>
       <c r="E59" s="3">
-        <v>17700</v>
+        <v>7000</v>
       </c>
       <c r="F59" s="3">
-        <v>17200</v>
+        <v>7300</v>
       </c>
       <c r="G59" s="3">
-        <v>15200</v>
+        <v>6800</v>
       </c>
       <c r="H59" s="3">
-        <v>14400</v>
+        <v>5700</v>
       </c>
       <c r="I59" s="3">
-        <v>13900</v>
+        <v>5400</v>
       </c>
       <c r="J59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K59" s="3">
         <v>16400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E60" s="3">
         <v>23200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>11400</v>
+      </c>
+      <c r="G61" s="3">
+        <v>12600</v>
+      </c>
+      <c r="H61" s="3">
+        <v>14800</v>
+      </c>
+      <c r="I61" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K61" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N61" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O61" s="3">
+        <v>8000</v>
+      </c>
+      <c r="P61" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>5000</v>
       </c>
-      <c r="E61" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>7000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>6000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>8000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>6000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L62" s="3">
         <v>3800</v>
       </c>
-      <c r="H62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>3800</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3073,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3120,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3167,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E66" s="3">
         <v>30800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>35500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3233,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3280,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3327,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3374,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3421,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-69900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-73000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-74700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-74500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-30800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-28000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-26200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-29900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-34600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3515,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3562,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3609,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E76" s="3">
         <v>43200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>88100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>93500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>98100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>101700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>102800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3703,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-2200</v>
+        <v>3100</v>
       </c>
       <c r="E81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
-        <v>-47600</v>
-      </c>
       <c r="G81" s="3">
-        <v>-6700</v>
+        <v>-43700</v>
       </c>
       <c r="H81" s="3">
-        <v>-5700</v>
+        <v>-2700</v>
       </c>
       <c r="I81" s="3">
-        <v>-4300</v>
+        <v>-1800</v>
       </c>
       <c r="J81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3821,55 +4022,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>3800</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>4200</v>
+        <v>1300</v>
       </c>
       <c r="G83" s="3">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>3500</v>
+        <v>1400</v>
       </c>
       <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>3100</v>
       </c>
       <c r="M83" s="3">
         <v>3100</v>
       </c>
       <c r="N83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3915,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3962,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4009,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4056,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4103,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E89" s="3">
         <v>4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4169,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-1600</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
-        <v>-1900</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-2300</v>
+        <v>-300</v>
       </c>
       <c r="G91" s="3">
-        <v>-3200</v>
+        <v>-400</v>
       </c>
       <c r="H91" s="3">
-        <v>-3000</v>
+        <v>-1100</v>
       </c>
       <c r="I91" s="3">
-        <v>-3000</v>
+        <v>-800</v>
       </c>
       <c r="J91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-2800</v>
       </c>
       <c r="M91" s="3">
         <v>-2800</v>
       </c>
       <c r="N91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4263,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4310,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-3000</v>
       </c>
       <c r="I94" s="3">
         <v>-3000</v>
       </c>
       <c r="J94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-2800</v>
       </c>
       <c r="M94" s="3">
         <v>-2800</v>
       </c>
       <c r="N94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4376,31 +4612,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4423,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4470,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4517,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4564,145 +4810,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F101" s="3">
-        <v>400</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H101" s="3">
         <v>200</v>
       </c>
       <c r="I101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
+        <v>500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
-        <v>500</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>CCLD</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E8" s="3">
         <v>28500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>15200</v>
       </c>
       <c r="F9" s="3">
         <v>15200</v>
       </c>
       <c r="G9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="H9" s="3">
         <v>17000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E10" s="3">
         <v>13100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>11900</v>
       </c>
       <c r="J10" s="3">
         <v>11900</v>
       </c>
       <c r="K10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="L10" s="3">
         <v>12900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1200</v>
       </c>
       <c r="L12" s="3">
         <v>1200</v>
       </c>
       <c r="M12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1018,96 +1037,102 @@
         <v>100</v>
       </c>
       <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>42700</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>100</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E15" s="3">
         <v>3200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3000</v>
       </c>
       <c r="K15" s="3">
         <v>3000</v>
       </c>
       <c r="L15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M15" s="3">
         <v>2800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2900</v>
       </c>
       <c r="N15" s="3">
         <v>2900</v>
       </c>
       <c r="O15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P15" s="3">
         <v>2700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E17" s="3">
         <v>25200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>34500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="3">
         <v>3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1243,119 +1275,126 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>6600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>400</v>
@@ -1364,13 +1403,13 @@
         <v>400</v>
       </c>
       <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1382,10 +1421,10 @@
         <v>100</v>
       </c>
       <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3">
         <v>200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -1393,58 +1432,64 @@
       <c r="R22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-44300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1458,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
@@ -1470,31 +1515,34 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-43700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-47600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-43700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-43700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2138,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2238,63 +2327,69 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E43" s="3">
         <v>16600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E44" s="3">
         <v>500</v>
@@ -2309,13 +2404,13 @@
         <v>500</v>
       </c>
       <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
-      </c>
-      <c r="K44" s="3">
-        <v>400</v>
       </c>
       <c r="L44" s="3">
         <v>400</v>
@@ -2327,19 +2422,22 @@
         <v>400</v>
       </c>
       <c r="O44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P44" s="3">
         <v>500</v>
       </c>
       <c r="Q44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -2356,90 +2454,96 @@
         <v>0</v>
       </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
         <v>0</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>4800</v>
       </c>
       <c r="Q45" s="3">
         <v>4800</v>
       </c>
       <c r="R45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="S45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E46" s="3">
         <v>22700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>37600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>36800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2464,8 +2568,8 @@
       <c r="J47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2488,108 +2592,117 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E49" s="3">
         <v>39300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>42400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>44300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>87900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>89100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>89700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>90700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>90900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>91400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>91700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>92000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>92800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>93900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2688,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -2700,22 +2819,22 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>800</v>
       </c>
       <c r="L52" s="3">
         <v>800</v>
@@ -2724,22 +2843,25 @@
         <v>800</v>
       </c>
       <c r="N52" s="3">
+        <v>800</v>
+      </c>
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2788,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E54" s="3">
         <v>70700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>74000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>77800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>125900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>126800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>131000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>136200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>131200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>140100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>141200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>140800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>142500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>143400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2878,208 +3007,221 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
         <v>5600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5200</v>
       </c>
       <c r="J57" s="3">
         <v>5200</v>
       </c>
       <c r="K57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>7000</v>
+        <v>6700</v>
       </c>
       <c r="E59" s="3">
         <v>7000</v>
       </c>
       <c r="F59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E60" s="3">
         <v>21900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
@@ -3087,49 +3229,52 @@
         <v>1900</v>
       </c>
       <c r="E61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F61" s="3">
         <v>7100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>7000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
@@ -3154,32 +3299,35 @@
       <c r="J62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3328,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E66" s="3">
         <v>24200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3598,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-69900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-73000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-74700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-74500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-30800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-28000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-26200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-27200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-29900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-31100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-36100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3798,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E76" s="3">
         <v>46500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>41700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>88100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>93500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>98100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>101700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>102800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>102300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>97900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-43700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4023,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>-2700</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
       </c>
       <c r="F83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>3100</v>
       </c>
       <c r="N83" s="3">
         <v>3100</v>
       </c>
       <c r="O83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P83" s="3">
         <v>2800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E89" s="3">
         <v>7100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4393,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-800</v>
       </c>
       <c r="J91" s="3">
         <v>-800</v>
       </c>
       <c r="K91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-2800</v>
       </c>
       <c r="N91" s="3">
         <v>-2800</v>
       </c>
       <c r="O91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4543,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-3000</v>
       </c>
       <c r="J94" s="3">
         <v>-3000</v>
       </c>
       <c r="K94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L94" s="3">
         <v>-2600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-2800</v>
       </c>
       <c r="N94" s="3">
         <v>-2800</v>
       </c>
       <c r="O94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P94" s="3">
         <v>-3300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -4639,8 +4872,8 @@
       <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4813,154 +5055,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>CCLD</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E8" s="3">
         <v>28200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E9" s="3">
         <v>15000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>15200</v>
       </c>
       <c r="G9" s="3">
         <v>15200</v>
       </c>
       <c r="H9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I9" s="3">
         <v>17000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>22700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E10" s="3">
         <v>13200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>11900</v>
       </c>
       <c r="K10" s="3">
         <v>11900</v>
       </c>
       <c r="L10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="M10" s="3">
         <v>12900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1200</v>
       </c>
       <c r="M12" s="3">
         <v>1200</v>
       </c>
       <c r="N12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1040,46 +1060,49 @@
         <v>100</v>
       </c>
       <c r="G14" s="3">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>42700</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>100</v>
       </c>
       <c r="L14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1087,52 +1110,55 @@
         <v>3300</v>
       </c>
       <c r="E15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F15" s="3">
         <v>3200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3000</v>
       </c>
       <c r="L15" s="3">
         <v>3000</v>
       </c>
       <c r="M15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N15" s="3">
         <v>2800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>2900</v>
       </c>
       <c r="O15" s="3">
         <v>2900</v>
       </c>
       <c r="P15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E17" s="3">
         <v>24700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>34500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1276,114 +1309,121 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E21" s="3">
         <v>6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1391,13 +1431,13 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -1406,13 +1446,13 @@
         <v>400</v>
       </c>
       <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1424,10 +1464,10 @@
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
@@ -1435,61 +1475,67 @@
       <c r="S22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-44300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1506,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -1518,31 +1564,34 @@
         <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-43700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-47600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-43700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-43700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2330,61 +2420,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E43" s="3">
         <v>17100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
@@ -2392,7 +2488,7 @@
         <v>600</v>
       </c>
       <c r="E44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F44" s="3">
         <v>500</v>
@@ -2407,13 +2503,13 @@
         <v>500</v>
       </c>
       <c r="J44" s="3">
+        <v>500</v>
+      </c>
+      <c r="K44" s="3">
         <v>400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>300</v>
-      </c>
-      <c r="L44" s="3">
-        <v>400</v>
       </c>
       <c r="M44" s="3">
         <v>400</v>
@@ -2425,24 +2521,27 @@
         <v>400</v>
       </c>
       <c r="P44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q44" s="3">
         <v>500</v>
       </c>
       <c r="R44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -2457,93 +2556,99 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>4800</v>
       </c>
       <c r="R45" s="3">
         <v>4800</v>
       </c>
       <c r="S45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="T45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E46" s="3">
         <v>24800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>31500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>34900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2571,8 +2676,8 @@
       <c r="K47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2595,8 +2700,11 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
@@ -2604,105 +2712,111 @@
         <v>8400</v>
       </c>
       <c r="E48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F48" s="3">
         <v>8200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E49" s="3">
         <v>37900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>39300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>40700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>44300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>87900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>89100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>89700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>90700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>90900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>91400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>91700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>92000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>92800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>93900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2807,8 +2924,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -2822,22 +2942,22 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>800</v>
@@ -2846,22 +2966,25 @@
         <v>800</v>
       </c>
       <c r="O52" s="3">
+        <v>800</v>
+      </c>
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E54" s="3">
         <v>71600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>74000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>76900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>77800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>125900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>126800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>131000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>136200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>131200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>140100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>141200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>140800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>142500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>143400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3008,278 +3138,294 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5200</v>
       </c>
       <c r="K57" s="3">
         <v>5200</v>
       </c>
       <c r="L57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>600</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>7000</v>
       </c>
       <c r="F59" s="3">
         <v>7000</v>
       </c>
       <c r="G59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H59" s="3">
         <v>7300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>22200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>23300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E60" s="3">
         <v>19600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E61" s="3">
         <v>1900</v>
       </c>
       <c r="F61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G61" s="3">
         <v>7100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>7000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>91</v>
+      <c r="D62" s="3">
+        <v>100</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>91</v>
@@ -3302,32 +3448,35 @@
       <c r="K62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M62" s="3">
         <v>4100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E66" s="3">
         <v>21800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>45500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-64700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-66600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-69900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-73000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-74700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-74500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-28000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-29900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-34600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-36100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E76" s="3">
         <v>49800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>46500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>43200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>41400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>88100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>93500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>101700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>102800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>102700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>102300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>97900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>97800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-43700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>-2700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1100</v>
       </c>
       <c r="F83" s="3">
         <v>1100</v>
       </c>
       <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>3100</v>
       </c>
       <c r="O83" s="3">
         <v>3100</v>
       </c>
       <c r="P83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4613,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-800</v>
       </c>
       <c r="K91" s="3">
         <v>-800</v>
       </c>
       <c r="L91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2800</v>
       </c>
       <c r="O91" s="3">
         <v>-2800</v>
       </c>
       <c r="P91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-3000</v>
       </c>
       <c r="K94" s="3">
         <v>-3000</v>
       </c>
       <c r="L94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-2800</v>
       </c>
       <c r="O94" s="3">
         <v>-2800</v>
       </c>
       <c r="P94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -4875,8 +5109,8 @@
       <c r="K96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5058,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>CCLD</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E8" s="3">
         <v>27600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>35300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E9" s="3">
         <v>15500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>15200</v>
       </c>
       <c r="H9" s="3">
         <v>15200</v>
       </c>
       <c r="I9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J9" s="3">
         <v>17000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E10" s="3">
         <v>12200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>11900</v>
       </c>
       <c r="L10" s="3">
         <v>11900</v>
       </c>
       <c r="M10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="N10" s="3">
         <v>12900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1200</v>
       </c>
       <c r="N12" s="3">
         <v>1200</v>
       </c>
       <c r="O12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,13 +1062,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1063,102 +1083,108 @@
         <v>100</v>
       </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>42700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>100</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="E15" s="3">
         <v>3300</v>
       </c>
       <c r="F15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G15" s="3">
         <v>3200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3000</v>
       </c>
       <c r="M15" s="3">
         <v>3000</v>
       </c>
       <c r="N15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O15" s="3">
         <v>2800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2900</v>
       </c>
       <c r="P15" s="3">
         <v>2900</v>
       </c>
       <c r="Q15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R15" s="3">
         <v>2700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E17" s="3">
         <v>25500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1310,8 +1343,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1319,111 +1353,117 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E21" s="3">
         <v>5500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1434,13 +1474,13 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
@@ -1449,13 +1489,13 @@
         <v>400</v>
       </c>
       <c r="K22" s="3">
+        <v>400</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1467,10 +1507,10 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-44300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1555,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
@@ -1567,31 +1613,34 @@
         <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-43700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-47600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1982,8 +2049,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -1991,111 +2061,117 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-43700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-43700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2423,75 +2513,81 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E43" s="3">
         <v>18300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>21700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>600</v>
       </c>
       <c r="F44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>500</v>
@@ -2506,13 +2602,13 @@
         <v>500</v>
       </c>
       <c r="K44" s="3">
+        <v>500</v>
+      </c>
+      <c r="L44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300</v>
-      </c>
-      <c r="M44" s="3">
-        <v>400</v>
       </c>
       <c r="N44" s="3">
         <v>400</v>
@@ -2524,28 +2620,31 @@
         <v>400</v>
       </c>
       <c r="Q44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R44" s="3">
         <v>500</v>
       </c>
       <c r="S44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
       <c r="F45" s="3">
         <v>0</v>
       </c>
@@ -2559,96 +2658,102 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4000</v>
-      </c>
-      <c r="R45" s="3">
-        <v>4800</v>
       </c>
       <c r="S45" s="3">
         <v>4800</v>
       </c>
       <c r="T45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="U45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E46" s="3">
         <v>28600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>31500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>35600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>34900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2679,8 +2784,8 @@
       <c r="L47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2703,120 +2808,129 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>8400</v>
+        <v>8900</v>
       </c>
       <c r="E48" s="3">
         <v>8400</v>
       </c>
       <c r="F48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G48" s="3">
         <v>8200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E49" s="3">
         <v>36100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>44300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>87900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>89100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>89700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>90700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>90900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>91400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>91700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>92000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>92800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>93900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2927,13 +3044,16 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -2945,22 +3065,22 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>800</v>
       </c>
       <c r="N52" s="3">
         <v>800</v>
@@ -2969,22 +3089,25 @@
         <v>800</v>
       </c>
       <c r="P52" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E54" s="3">
         <v>73600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>77800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>125900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>126800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>131000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>136200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>131200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>140100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>141200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>140800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>142500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>143400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3139,64 +3269,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>5000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>5200</v>
       </c>
       <c r="L57" s="3">
         <v>5200</v>
       </c>
       <c r="M57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
@@ -3204,231 +3338,243 @@
         <v>1500</v>
       </c>
       <c r="E58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>600</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>7000</v>
       </c>
       <c r="G59" s="3">
         <v>7000</v>
       </c>
       <c r="H59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I59" s="3">
         <v>7300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E60" s="3">
         <v>16900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1900</v>
       </c>
       <c r="F61" s="3">
         <v>1900</v>
       </c>
       <c r="G61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H61" s="3">
         <v>7100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>7000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>91</v>
@@ -3451,32 +3597,35 @@
       <c r="L62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E66" s="3">
         <v>19400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>42900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>45500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-64700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-66600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-69900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-73000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-74700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-74500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-30800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-28000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-31100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-34600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-36100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E76" s="3">
         <v>54200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>88100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>93500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>98100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>101700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>102800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>102700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>97900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>97000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>97800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-43700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
@@ -4429,55 +4628,58 @@
         <v>1100</v>
       </c>
       <c r="E83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F83" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>3100</v>
       </c>
       <c r="P83" s="3">
         <v>3100</v>
       </c>
       <c r="Q83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="R83" s="3">
         <v>2800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E89" s="3">
         <v>5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-800</v>
       </c>
       <c r="L91" s="3">
         <v>-800</v>
       </c>
       <c r="M91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-2800</v>
       </c>
       <c r="P91" s="3">
         <v>-2800</v>
       </c>
       <c r="Q91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-3000</v>
       </c>
       <c r="L94" s="3">
         <v>-3000</v>
       </c>
       <c r="M94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-2800</v>
       </c>
       <c r="P94" s="3">
         <v>-2800</v>
       </c>
       <c r="Q94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -5112,8 +5346,8 @@
       <c r="L96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>CCLD</t>
   </si>
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E8" s="3">
         <v>31100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>27600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>28400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>29300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E9" s="3">
         <v>16200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>15200</v>
       </c>
       <c r="J9" s="3">
         <v>15200</v>
       </c>
       <c r="K9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="L9" s="3">
         <v>17000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E10" s="3">
         <v>14800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>11900</v>
       </c>
       <c r="N10" s="3">
         <v>11900</v>
       </c>
       <c r="O10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="P10" s="3">
         <v>12900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1200</v>
       </c>
       <c r="P12" s="3">
         <v>1200</v>
       </c>
       <c r="Q12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R12" s="3">
         <v>1100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1097,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
         <v>100</v>
@@ -1109,108 +1128,114 @@
         <v>100</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>42700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>100</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E15" s="3">
         <v>4000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3300</v>
       </c>
       <c r="G15" s="3">
         <v>3300</v>
       </c>
       <c r="H15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>3000</v>
       </c>
       <c r="O15" s="3">
         <v>3000</v>
       </c>
       <c r="P15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2800</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>2900</v>
       </c>
       <c r="R15" s="3">
         <v>2900</v>
       </c>
       <c r="S15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="T15" s="3">
         <v>2700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E17" s="3">
         <v>27800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E18" s="3">
         <v>3200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1378,70 +1410,74 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1449,66 +1485,69 @@
         <v>7200</v>
       </c>
       <c r="E21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F21" s="3">
         <v>6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1520,13 +1559,13 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
@@ -1535,13 +1574,13 @@
         <v>400</v>
       </c>
       <c r="M22" s="3">
+        <v>400</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -1553,10 +1592,10 @@
         <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
@@ -1564,75 +1603,81 @@
       <c r="V22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1653,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
@@ -1665,31 +1710,34 @@
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-43700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-47600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-43700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-43700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2485,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2609,87 +2698,93 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E43" s="3">
         <v>19300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>21700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I44" s="3">
         <v>500</v>
@@ -2704,13 +2799,13 @@
         <v>500</v>
       </c>
       <c r="M44" s="3">
+        <v>500</v>
+      </c>
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>300</v>
-      </c>
-      <c r="O44" s="3">
-        <v>400</v>
       </c>
       <c r="P44" s="3">
         <v>400</v>
@@ -2722,19 +2817,22 @@
         <v>400</v>
       </c>
       <c r="S44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T44" s="3">
         <v>500</v>
       </c>
       <c r="U44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -2745,11 +2843,11 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
@@ -2763,102 +2861,108 @@
         <v>0</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4000</v>
-      </c>
-      <c r="T45" s="3">
-        <v>4800</v>
       </c>
       <c r="U45" s="3">
         <v>4800</v>
       </c>
       <c r="V45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="W45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E46" s="3">
         <v>29300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>27500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>36800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>35600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>36400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>34900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -2895,8 +2999,8 @@
       <c r="N47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2919,132 +3023,141 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>8400</v>
       </c>
       <c r="G48" s="3">
         <v>8400</v>
       </c>
       <c r="H48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I48" s="3">
         <v>8200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E49" s="3">
         <v>51700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>37900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>39300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>40700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>42400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>44300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>87900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>89100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>89700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>90700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>90900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>91400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>91700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>92000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>92800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>93900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3167,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -3176,10 +3295,10 @@
         <v>400</v>
       </c>
       <c r="E52" s="3">
+        <v>400</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
@@ -3191,22 +3310,22 @@
         <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>800</v>
       </c>
       <c r="P52" s="3">
         <v>800</v>
@@ -3215,22 +3334,25 @@
         <v>800</v>
       </c>
       <c r="R52" s="3">
+        <v>800</v>
+      </c>
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E54" s="3">
         <v>90600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>74000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>125900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>126800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>131000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>136200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>131200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>140100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>141200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>140800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>142500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>143400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3401,332 +3530,348 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>5200</v>
       </c>
       <c r="N57" s="3">
         <v>5200</v>
       </c>
       <c r="O57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1500</v>
       </c>
       <c r="F58" s="3">
         <v>1500</v>
       </c>
       <c r="G58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H58" s="3">
         <v>1600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>600</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E59" s="3">
         <v>6100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>7000</v>
       </c>
       <c r="I59" s="3">
         <v>7000</v>
       </c>
       <c r="J59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K59" s="3">
         <v>7300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E60" s="3">
         <v>23200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E61" s="3">
         <v>8400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1900</v>
       </c>
       <c r="H61" s="3">
         <v>1900</v>
       </c>
       <c r="I61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J61" s="3">
         <v>7100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>7000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
       </c>
       <c r="F62" s="3">
+        <v>400</v>
+      </c>
+      <c r="G62" s="3">
         <v>100</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>91</v>
@@ -3749,32 +3894,35 @@
       <c r="N62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P62" s="3">
         <v>4100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E66" s="3">
         <v>32800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>42900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>45500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-58700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-61800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-64700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-66600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-69900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-73000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-74700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-74500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-28000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-26200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-29900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-31100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-34600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-36100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E76" s="3">
         <v>57800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>56100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>54200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>88100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>93500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>98100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>101700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>102800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>102700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>102300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>97900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>97000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>97800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-43700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4818,13 +5015,14 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>-6700</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
@@ -4833,55 +5031,58 @@
         <v>1100</v>
       </c>
       <c r="G83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H83" s="3">
         <v>-2700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
       </c>
       <c r="J83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3100</v>
       </c>
       <c r="R83" s="3">
         <v>3100</v>
       </c>
       <c r="S83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="T83" s="3">
         <v>2800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>7400</v>
+        <v>8700</v>
       </c>
       <c r="E89" s="3">
         <v>7400</v>
       </c>
       <c r="F89" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G89" s="3">
         <v>5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -5276,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-800</v>
       </c>
       <c r="N91" s="3">
         <v>-800</v>
       </c>
       <c r="O91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-2800</v>
       </c>
       <c r="R91" s="3">
         <v>-2800</v>
       </c>
       <c r="S91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="T91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-3000</v>
       </c>
       <c r="N94" s="3">
         <v>-3000</v>
       </c>
       <c r="O94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-2800</v>
       </c>
       <c r="R94" s="3">
         <v>-2800</v>
       </c>
       <c r="S94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="T94" s="3">
         <v>-3300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -5586,8 +5819,8 @@
       <c r="N96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5796,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E100" s="3">
         <v>4900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>CCLD</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E8" s="3">
         <v>34400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>27400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>28100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E9" s="3">
         <v>18300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>15200</v>
       </c>
       <c r="K9" s="3">
         <v>15200</v>
       </c>
       <c r="L9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="M9" s="3">
         <v>17000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E10" s="3">
         <v>16100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>11900</v>
       </c>
       <c r="O10" s="3">
         <v>11900</v>
       </c>
       <c r="P10" s="3">
+        <v>11900</v>
+      </c>
+      <c r="Q10" s="3">
         <v>12900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>14200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E12" s="3">
         <v>2500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1200</v>
       </c>
       <c r="Q12" s="3">
         <v>1200</v>
       </c>
       <c r="R12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S12" s="3">
         <v>1100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,13 +1121,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1119,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>100</v>
@@ -1131,111 +1151,117 @@
         <v>100</v>
       </c>
       <c r="K14" s="3">
+        <v>100</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>42700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3300</v>
       </c>
       <c r="H15" s="3">
         <v>3300</v>
       </c>
       <c r="I15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3300</v>
-      </c>
-      <c r="O15" s="3">
-        <v>3000</v>
       </c>
       <c r="P15" s="3">
         <v>3000</v>
       </c>
       <c r="Q15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R15" s="3">
         <v>2800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>2900</v>
       </c>
       <c r="S15" s="3">
         <v>2900</v>
       </c>
       <c r="T15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="U15" s="3">
         <v>2700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E17" s="3">
         <v>31300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>30500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>30100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>36900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31500</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E18" s="3">
         <v>3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,146 +1444,153 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>7200</v>
+        <v>5100</v>
       </c>
       <c r="E21" s="3">
         <v>7200</v>
       </c>
       <c r="F21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G21" s="3">
         <v>6400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1562,13 +1602,13 @@
         <v>100</v>
       </c>
       <c r="I22" s="3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
@@ -1577,13 +1617,13 @@
         <v>400</v>
       </c>
       <c r="N22" s="3">
+        <v>400</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -1595,10 +1635,10 @@
         <v>100</v>
       </c>
       <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
@@ -1606,73 +1646,79 @@
       <c r="W22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-44300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1680,7 +1726,7 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1701,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
@@ -1713,31 +1759,34 @@
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-43700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-47600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-43700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-43700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
@@ -2710,84 +2803,87 @@
         <v>18700</v>
       </c>
       <c r="E43" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F43" s="3">
         <v>19300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>21700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>22800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>21700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>400</v>
+      </c>
+      <c r="E44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>600</v>
       </c>
       <c r="I44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J44" s="3">
         <v>500</v>
@@ -2802,13 +2898,13 @@
         <v>500</v>
       </c>
       <c r="N44" s="3">
+        <v>500</v>
+      </c>
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
-      </c>
-      <c r="P44" s="3">
-        <v>400</v>
       </c>
       <c r="Q44" s="3">
         <v>400</v>
@@ -2820,19 +2916,22 @@
         <v>400</v>
       </c>
       <c r="T44" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U44" s="3">
         <v>500</v>
       </c>
       <c r="V44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W44" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -2843,14 +2942,14 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
@@ -2864,105 +2963,111 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4000</v>
-      </c>
-      <c r="U45" s="3">
-        <v>4800</v>
       </c>
       <c r="V45" s="3">
         <v>4800</v>
       </c>
       <c r="W45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="X45" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E46" s="3">
         <v>25700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>27500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>35600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>36400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>34900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
@@ -3002,8 +3107,8 @@
       <c r="O47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3026,138 +3131,147 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E48" s="3">
         <v>10900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>8400</v>
       </c>
       <c r="H48" s="3">
         <v>8400</v>
       </c>
       <c r="I48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J48" s="3">
         <v>8200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E49" s="3">
         <v>50400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>51700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>37900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>39300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>42400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>44300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>87900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>89100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>89700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>90700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>90900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>91400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>91700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>92000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>92800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>93900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3286,22 +3403,25 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
       <c r="F52" s="3">
+        <v>400</v>
+      </c>
+      <c r="G52" s="3">
         <v>300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -3313,22 +3433,22 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>800</v>
       </c>
       <c r="Q52" s="3">
         <v>800</v>
@@ -3337,22 +3457,25 @@
         <v>800</v>
       </c>
       <c r="S52" s="3">
+        <v>800</v>
+      </c>
+      <c r="T52" s="3">
         <v>900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E54" s="3">
         <v>87600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>90600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>75200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>125900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>126800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>131000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>136200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>131200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>140100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>141200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>140800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>142500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>143400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3531,350 +3661,366 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E57" s="3">
         <v>6900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>5200</v>
       </c>
       <c r="O57" s="3">
         <v>5200</v>
       </c>
       <c r="P57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1500</v>
       </c>
       <c r="G58" s="3">
         <v>1500</v>
       </c>
       <c r="H58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I58" s="3">
         <v>1600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>600</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>600</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E59" s="3">
         <v>5700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>7000</v>
       </c>
       <c r="J59" s="3">
         <v>7000</v>
       </c>
       <c r="K59" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L59" s="3">
         <v>7300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>22200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E60" s="3">
         <v>24400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>28100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1900</v>
       </c>
       <c r="I61" s="3">
         <v>1900</v>
       </c>
       <c r="J61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K61" s="3">
         <v>7100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>7000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
       </c>
       <c r="F62" s="3">
         <v>400</v>
       </c>
       <c r="G62" s="3">
+        <v>400</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>91</v>
@@ -3897,32 +4043,35 @@
       <c r="O62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q62" s="3">
         <v>4100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E66" s="3">
         <v>28100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>42900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>45600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-55800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-58700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-61800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-64700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-66600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-69900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-73000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-74700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-74500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-28000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-26100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-29900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-31100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-34600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-36100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E76" s="3">
         <v>59500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>56100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>54200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>88100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>93500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>98100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>101700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>102800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>102700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>102300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>97900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>97000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>97800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>103500</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-43700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -5016,16 +5214,17 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>-6700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1100</v>
       </c>
       <c r="F83" s="3">
         <v>1100</v>
@@ -5034,55 +5233,58 @@
         <v>1100</v>
       </c>
       <c r="H83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I83" s="3">
         <v>-2700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1100</v>
       </c>
       <c r="J83" s="3">
         <v>1100</v>
       </c>
       <c r="K83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3100</v>
       </c>
       <c r="S83" s="3">
         <v>3100</v>
       </c>
       <c r="T83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U83" s="3">
         <v>2800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E89" s="3">
         <v>8700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>7400</v>
       </c>
       <c r="F89" s="3">
         <v>7400</v>
       </c>
       <c r="G89" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H89" s="3">
         <v>5100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-800</v>
       </c>
       <c r="O91" s="3">
         <v>-800</v>
       </c>
       <c r="P91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-2800</v>
       </c>
       <c r="S91" s="3">
         <v>-2800</v>
       </c>
       <c r="T91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3200</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-3000</v>
       </c>
       <c r="O94" s="3">
         <v>-3000</v>
       </c>
       <c r="P94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-2800</v>
       </c>
       <c r="S94" s="3">
         <v>-2800</v>
       </c>
       <c r="T94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -5822,8 +6056,8 @@
       <c r="O96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
@@ -6115,125 +6364,131 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
     </row>
